--- a/claims_log.xlsx
+++ b/claims_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,113 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>POL-2026-30099</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Mehta</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 to 31-Dec-2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Minor scratch on parked car door.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Mehta</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>arjun.mehta@email.com, +91-9812345671</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>KA-03-XZ-7799</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle Damage</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>photo.jpg</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Fast-track</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Fast-track because estimated damage (₹9,000.00) is below the ₹25,000 threshold and no other flags were triggered.</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 15:26:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
